--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_670_Saint_Vincent_the_Grenadines.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_670_Saint_Vincent_the_Grenadines.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re5b5fb4ca5ef4cee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rccff7e24cf624a9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R95f88e18f91b4f7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7fbd1f13d20d41ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R26e410607b6644c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R45baac5faedc4a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R078d14ebd43b4f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb54b4e04904b4e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1c45b5cecd71489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Refcb82b9ac3e4cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8ada918c5bb4407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R380dd80223394515"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ670CommercialTable" displayName="EEZ670CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ670CommercialTable" displayName="EEZ670CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ670FunctionalTable" displayName="EEZ670FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ670FunctionalTable" displayName="EEZ670FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ670ValidationTable" displayName="EEZ670ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ670ValidationTable" displayName="EEZ670ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6925,7 +6879,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re69b9d6d6be5482f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ce0c7d1d83d4bf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6935,20 +6889,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6956,552 +6900,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.524168632</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.524168632</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$94,A2,'Species'!$U$2:$U$94))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>83.07512965584549</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>83.07512965584549</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>90.15631978900001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.1999692773490924</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>158.4781078676412</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>90.15631978900001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>158.47884748544794</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$94,A3,'Species'!$U$2:$U$94))</x:f>
-        <x:v>14287.869653690204</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.1999692773490924</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>158.4781078676412</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>14287.802972470698</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0.06668121950679051</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.000004667003012</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.000004667003011958511</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.0021977896</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.77</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>588.843655355589</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.0021977896</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>588.843655355589</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$94,A4,'Species'!$U$2:$U$94))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1.294154461766498</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.77</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>588.843655355589</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>1.294154461766498</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2.8404086308999994</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3841778620378444</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>242.20207640300637</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2.8404086308999994</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>276.44785389985964</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$94,A5,'Species'!$U$2:$U$94))</x:f>
-        <x:v>785.2248702109433</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3841778620378444</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>242.20207640300637</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>687.9528682370004</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>97.2720019739429</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.14139341002127</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.14139341002126996</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>223.7580623267</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1899841395680535</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>15.487600571714141</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>223.7580623267</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>15.4876930552772</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$94,A6,'Species'!$U$2:$U$94))</x:f>
-        <x:v>3465.496187959515</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1899841395680535</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>15.487600571714141</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3465.4754940166476</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.02069394286718307</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0000059714584342</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.000005971458434178054</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>243.88561926469998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2404829026512427</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>173.97342066592296</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>243.88561926469998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>204.44024075393224</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$94,A7,'Species'!$U$2:$U$94))</x:f>
-        <x:v>49860.03471889712</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2404829026512427</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>173.97342066592296</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>42429.61543470677</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>7430.41928419035</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1751234181140464</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1751234181140464</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>882.8221688563001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8329353922834044</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>680.6680917326554</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>882.8221688563001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1026.0902199641876</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$94,A8,'Species'!$U$2:$U$94))</x:f>
-        <x:v>905855.1934310221</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8329353922834044</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>680.6680917326554</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>600908.8810147019</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>304946.3124163202</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5074751298422886</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5074751298422886</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>24.5396861419</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.402141425402393</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2524.3026627266568</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>24.5396861419</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2675.9441677745162</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$94,A9,'Species'!$U$2:$U$94))</x:f>
-        <x:v>65666.83001043442</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.402141425402393</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2524.3026627266568</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>61945.59507047461</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3721.234939959817</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0600726320527911</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.060072632052791196</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>226.2619736568</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.494062601178597</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>3119.339187403501</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>226.2619736568</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>3125.385849559824</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$94,A10,'Species'!$U$2:$U$94))</x:f>
-        <x:v>707155.9707604403</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.494062601178597</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>3119.339187403501</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>705787.8410469148</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1368.12971352553</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0019384433025882</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0019384433025881331</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b81f720b39148a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fbe213bcb4040bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7511,20 +7096,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7532,876 +7107,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2.5278421862</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.480123093041449</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>3020.807793282525</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2.5278421862</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>3060.7647799282186</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$94,A2,'Species'!$U$2:$U$94))</x:f>
-        <x:v>7737.13033273771</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.480123093041449</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>3020.807793282525</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7636.125376261295</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>101.00495647641492</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0132272522384733</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.013227252238473292</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>362.32639603279995</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.435451419890124</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2725.532844216922</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>362.32639603279995</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2790.2607797295623</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$94,A3,'Species'!$U$2:$U$94))</x:f>
-        <x:v>1010985.1323110826</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.435451419890124</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2725.532844216922</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>987532.4927141442</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>23452.63959693839</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0237487270241417</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.023748727024141675</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.11728503059999999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.11728503059999999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$94,A4,'Species'!$U$2:$U$94))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>28.134719231148818</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>28.134719231148818</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4.4464720198</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.386475107092499</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2434.8662341975596</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4.4464720198</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2588.997665113824</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$94,A5,'Species'!$U$2:$U$94))</x:f>
-        <x:v>11511.905677256149</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.386475107092499</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2434.8662341975596</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>10826.564582315243</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>685.3410949409063</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0633018063791337</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.06330180637913373</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>24.422401111299997</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.407050110990248</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2552.995862632921</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>24.422401111299997</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2687.6429959555826</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$94,A6,'Species'!$U$2:$U$94))</x:f>
-        <x:v>65638.69529120327</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.407050110990248</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2552.995862632921</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>62350.28899271055</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3288.4062984927223</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0527408349122034</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.05274083491220344</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>90.15631978900001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.1999692773490924</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>158.4781078676412</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>90.15631978900001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>158.47884748544794</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$94,A7,'Species'!$U$2:$U$94))</x:f>
-        <x:v>14287.869653690204</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.1999692773490924</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>158.4781078676412</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>14287.802972470698</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.06668121950679051</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.000004667003012</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.000004667003011958511</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>6.8982065688</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.18</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1513.5612484362073</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>6.8982065688</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$94,A8,'Species'!$U$2:$U$94))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10440.858146243774</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.18</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>10440.858146243774</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>10.3383292605</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.387462078412588</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2440.405968146441</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>10.3383292605</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2601.1384321690603</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$94,A9,'Species'!$U$2:$U$94))</x:f>
-        <x:v>26891.42556390449</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.387462078412588</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2440.405968146441</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>25229.72042798718</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1661.7051359173092</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.065863002353129</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.06586300235312911</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>197.4746605654</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.302597701337504</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>200.7232597602015</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>197.4746605654</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>216.78646314437822</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$94,A10,'Species'!$U$2:$U$94))</x:f>
-        <x:v>42809.83322460968</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.302597701337504</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>200.7232597602015</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>39637.7575887264</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3172.0756358832805</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0800266167626362</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.08002661676263614</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>383.0920196535</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.721185401401932</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>526.2418724180645</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>383.0920196535</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>637.3145130833049</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$94,A11,'Species'!$U$2:$U$94))</x:f>
-        <x:v>244150.1039715702</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.721185401401932</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>526.2418724180645</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>201599.06173087584</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>42551.04224069437</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2110676601139037</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2110676601139036</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>316.965503622</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9527705693615856</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>896.954822822011</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>316.965503622</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>965.9225305399906</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$94,A12,'Species'!$U$2:$U$94))</x:f>
-        <x:v>306164.1213524448</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9527705693615856</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>896.954822822011</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>284303.73714196053</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>21860.384210484277</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.07689094920187</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.07689094920186997</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>223.7580623267</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.1899841395680535</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>15.487600571714141</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>223.7580623267</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>15.4876930552772</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$94,A13,'Species'!$U$2:$U$94))</x:f>
-        <x:v>3465.496187959515</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.1899841395680535</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>15.487600571714141</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>3465.4754940166476</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0.02069394286718307</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0000059714584342</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.000005971458434178054</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>3.3645772628999997</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.355484730495413</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>226.71733634391393</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>3.3645772628999997</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>258.07105381149216</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$94,A14,'Species'!$U$2:$U$94))</x:f>
-        <x:v>868.2999998667889</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.355484730495413</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>226.71733634391393</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>762.8079949679845</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>105.49200489880434</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1382943094392082</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.1382943094392081</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>68.90033186880001</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.151096205415524</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>14.161074429715951</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>68.90033186880001</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>31.64989589111066</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$94,A15,'Species'!$U$2:$U$94))</x:f>
-        <x:v>2180.6883305104943</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.151096205415524</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>14.161074429715951</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>975.7027278262069</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1204.9856026842874</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>2.2349925528740764</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>1.2349925528740764</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>0.0021977896</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.77</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>588.843655355589</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>0.0021977896</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>588.843655355589</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$94,A16,'Species'!$U$2:$U$94))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1.294154461766498</x:v>
       </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.77</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>588.843655355589</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>1.294154461766498</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65214a0b20c3431a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144565a28157458e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8576,7 +7582,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8675,7 +7681,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1747160.9889167729</x:v>
+        <x:v>1429597.53318564</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8689,7 +7695,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1747160.9889167729</x:v>
+        <x:v>1649077.8247641998</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8703,7 +7709,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-317563.45573113323</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8717,7 +7723,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-98083.16415257333</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8728,9 +7734,9 @@
         <x:v>EEZ_670</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8742,47 +7748,19 @@
         <x:v>EEZ_670</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_670</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_670</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf22563483ee4c5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444773bace064625"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8829,7 +7807,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
